--- a/RHOAI-study-materials/2-RHOAI-Enablement-materials/RHOAI-HandsOn-v1.1/RHOAI-3.4-HandsOn-커리큘럼-v1.1.xlsx
+++ b/RHOAI-study-materials/2-RHOAI-Enablement-materials/RHOAI-HandsOn-v1.1/RHOAI-3.4-HandsOn-커리큘럼-v1.1.xlsx
@@ -10,12 +10,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Week 1 설치+서빙" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Week 2 ML+보안" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Week 3 운영+MaaS+GPU" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="환경 매핑" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="컨설턴트 역량 매핑" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변경점 vs v0.9" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="추가-스터디-GPU공유" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="운영관리-보강" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="추가-스터디-LLM-MLOps-CI-CD" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="컨설턴트 역량 매핑" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Week 4 GPU공유" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Week 5 LLM-MLOps-CI-CD" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Week 6 2GPU-TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Week 7 운영관리-보강" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변경점 vs v0.9" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -135,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -153,15 +153,16 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -528,14 +529,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="20" customWidth="1" style="8" min="1" max="1"/>
-    <col width="95" customWidth="1" style="8" min="2" max="2"/>
+    <col width="20" customWidth="1" style="10" min="1" max="1"/>
+    <col width="95" customWidth="1" style="10" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" s="8">
+    <row r="1" ht="17.25" customHeight="1" s="10">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Red Hat OpenShift AI 3.4 — 설치 포함 딜리버리 핸즈온 커리큘럼 v1.1</t>
@@ -598,7 +599,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>3주 (15일) — 하루 4~6시간 자율 실습 / W1: Day1-5, W2: Day6-10, W3: Day11-15</t>
+          <t>기본 3주(15일) + 선택 Week4 GPU공유 / Week5 LLM MLOps CI/CD / Week6 2GPU TP / Week7 운영관리 보강</t>
         </is>
       </c>
     </row>
@@ -626,7 +627,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="33" customHeight="1" s="8">
+    <row r="10" ht="33" customHeight="1" s="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>기준 환경</t>
@@ -638,7 +639,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="33" customHeight="1" s="8">
+    <row r="11" ht="33" customHeight="1" s="10">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>GPU 세션</t>
@@ -646,11 +647,11 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>홈랩 GPU worker 사용 가능. Day11-12,14는 GPU Operator/NFD/KMM 설치 후 홈랩 GPU에서 우선 수행하고, MIG 등 미지원 항목은 별도 GPU 랩에서 수행</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="33" customHeight="1" s="8">
+          <t>홈랩 GPU worker 사용 가능. Day11-12,14와 추가 Week4/Week6은 GPU Operator/NFD/KMM 설치 후 수행하며, Week6은 동일 worker의 물리 GPU 2장이 필요. Week7 Ray는 CPU 연산으로 멀티노드 배치만 검증</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="33" customHeight="1" s="10">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>서빙 모드</t>
@@ -670,7 +671,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>설치 / 서빙 / ML·파이프라인 / 보안·거버넌스 / 모니터링·MaaS·GPU</t>
+          <t>설치 / 서빙 / ML·파이프라인 / 보안·거버넌스 / 모니터링·MaaS·GPU / 인증·백업·운영관리</t>
         </is>
       </c>
     </row>
@@ -750,7 +751,7 @@
       <c r="A21" s="2" t="n"/>
       <c r="B21" s="2" t="n"/>
     </row>
-    <row r="22" ht="33" customHeight="1" s="8">
+    <row r="22" ht="33" customHeight="1" s="10">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>[ v0.9 → v1.1 주요 변경 ]</t>
@@ -782,7 +783,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="33" customHeight="1" s="8">
+    <row r="25" ht="33" customHeight="1" s="10">
       <c r="A25" s="2" t="inlineStr">
         <is>
           <t>③ 서빙모드</t>
@@ -815,6 +816,18 @@
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>세션별 고객질문 · llm-d/GuideLLM · GPU 공유 · AI500/AI267 매핑 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>⑥ 운영관리 보강</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>선택 Week7에 RHBK OIDC, OADP 1.6, Ray/Kueue, 관측·감사, Dashboard 커스터마이징, quota와 on-prem 확장 판단 추가</t>
         </is>
       </c>
     </row>
@@ -830,580 +843,331 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="8" customWidth="1" style="8" min="1" max="1"/>
-    <col width="9" customWidth="1" style="8" min="2" max="2"/>
-    <col width="30" customWidth="1" style="8" min="3" max="3"/>
-    <col width="64" customWidth="1" style="8" min="4" max="4"/>
-    <col width="26" customWidth="1" style="8" min="5" max="5"/>
-    <col width="28" customWidth="1" style="8" min="6" max="6"/>
-    <col width="16" customWidth="1" style="8" min="7" max="7"/>
-    <col width="7" customWidth="1" style="8" min="8" max="9"/>
-    <col width="40" customWidth="1" style="8" min="10" max="10"/>
+    <col width="18" customWidth="1" style="10" min="1" max="1"/>
+    <col width="34" customWidth="1" style="10" min="2" max="2"/>
+    <col width="40" customWidth="1" style="10" min="3" max="3"/>
+    <col width="46" customWidth="1" style="10" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="8">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>추가 스터디 — Tekton CI × KFP × Trainer v2 × Model Registry × Argo CD × KServe vLLM : "LLM을 훈련하고 검증해 Git으로 승격·롤백하라"</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20.1" customHeight="1" s="8">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Day</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>세션명</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>수행할 작업 (Hands-on)</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>예상 결과물</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>고객 상황 연결</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>환경</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>AI500</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>AI267</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="150" customHeight="1" s="8">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>사전</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>사전점검</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>LLM MLOps 운영 경계와 지원 범위 확인</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1. Tekton=CI, KFP=ML workflow, Trainer v2=GPU 학습, Argo CD=CD 역할 분리
-2. RHOAI/Trainer/KFP/KServe/GitOps API와 GPU 확인
-3. 단일 GPU에서 학습→staging→production 순차 실행 계획
-4. MaaS-vLLM TP는 운영 기본 경로에서 제외</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>지원 범위·아키텍처·검증 순서 확정</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>"LLM 학습부터 운영 배포까지 책임 경계를 어떻게 나누나?"</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>홈 OCP + GPU worker + S3/Gitea/Nexus</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>🔶</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>🔶</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>RHOAI 3.4 기준. KServe Standard vLLM 경로</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="150" customHeight="1" s="8">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Step 1</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>핸즈온</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>폐쇄망 LLM artifact 준비</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1. boto3와 전이 wheel을 Nexus hosted에 반입
-2. Qwen2.5 0.5B ModelCar에서 base model 추출
-3. base model과 24건 합성 SFT JSONL을 S3에 버전 고정
-4. digest와 object metadata 기록</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>재현 가능한 base model·dataset·Python wheel</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>"인터넷 없는 환경에서 모델과 패키지를 어떻게 재현하나?"</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Bastion + 5010 model registry + Nexus + S3</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>🔶</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>실제 ID/PW는 문서·Git에 기록 금지</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="150" customHeight="1" s="8">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Step 2</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>핸즈온</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>OpenShift Pipelines와 프로젝트 구성</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1. OpenShift Pipelines Operator 설치
-2. CI/학습, staging, production Namespace와 최소 RBAC 구성
-3. S3·registry·Gitea Secret을 명령으로 생성
-4. Kubernetes-native pipelineStore DSPA 생성</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Tekton/KFP/Trainer/serving 실행 기반</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>"CI와 환경별 배포 권한을 어떻게 분리하나?"</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>OCP cluster-admin + RHOAI</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>🔶</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>🔶</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Secret manifest는 공개 저장소에 두지 않음</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="150" customHeight="1" s="8">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Step 3</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>핸즈온</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Source와 GitOps 저장소 분리</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1. source repo에 코드·dataset·Containerfile·KFP DSL 작성
-2. GitOps repo에 pipelines/staging/production 구조 작성
-3. ServingRuntime만 초기 desired state로 등록
-4. 두 repo 기밀 검사 후 push</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>소스 저장소와 배포 선언 저장소</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>"애플리케이션 코드와 운영 선언을 왜 분리하나?"</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Gitea + Bastion</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>🔶</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>🔶</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>Tekton은 GitOps repo만 변경하고 ISVC 직접 적용 금지</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="150" customHeight="1" s="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Step 4</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>핸즈온</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Tekton CI와 Argo CD 연결</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1. Argo CD private repository Secret과 Application 3개 생성
-2. Tekton CI/promotion Pipeline과 EventListener 생성
-3. 수동 PipelineRun으로 단계별 검증
-4. Gitea main push webhook 연결</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>push→CI→GitOps 동기화 경로</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>"코드 push를 검증·빌드·배포 선언으로 연결하려면?"</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>OpenShift Pipelines + GitOps + Gitea</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>🔶</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>🔶</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>Generic Gitea webhook은 랩용. 운영은 서명 검증 필수</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="150" customHeight="1" s="8">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Step 5</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>핸즈온</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Image digest와 Kubernetes-native KFP 추적</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1. source commit과 training image digest 확인
-2. KFP CR compile 결과를 GitOps repo에 발행
-3. Argo CD가 Pipeline/PipelineVersion 동기화
-4. DSPA API에 Run 자동 생성</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>commit→image→PipelineVersion→Run 추적성</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>"어떤 코드와 이미지로 학습했는지 감사 가능하게 하려면?"</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Tekton + Argo CD + RHOAI AI Pipelines</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>🔶</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>Tekton Pipeline과 KFP Pipeline은 API와 역할이 다름</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="150" customHeight="1" s="8">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Step 6</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>핸즈온</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Trainer v2 LoRA 학습과 Registry 등록</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1. KFP component가 단일 GPU TrainJob 생성
-2. LoRA 학습 후 merged model/adapter/metrics를 S3에 저장
-3. KFP scalar metrics와 S3 metrics 비교
-4. Model Registry에 stage=Staging version 자동 등록</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>TrainJob·모델 산출물·지표·Registry version</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>"학습 결과와 지표, 소스 commit을 하나의 모델 버전으로 묶으려면?"</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>GPU worker + Trainer v2 + S3 + Model Registry</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>🔶</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>작은 합성 dataset은 경로 검증용이며 품질 기준 아님</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="150" customHeight="1" s="8">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Step 7</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>핸즈온</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Staging gate와 KServe vLLM 검증</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1. Registry Staging과 train_loss gate 확인
-2. Tekton이 staging Git 선언 갱신
-3. Argo CD가 KServe Standard ISVC 배포
-4. OpenAI chat completions 호출과 추적정보 확인
-5. 실패 gate에서 Git 미변경 확인</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>승인 gate를 통과한 staging vLLM endpoint</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>"검증되지 않은 모델의 배포를 어떻게 차단하나?"</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Tekton + Argo CD + KServe + GPU</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>🔶</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>🔶</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>단일 GPU이므로 학습 종료 후 서빙</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="150" customHeight="1" s="8">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Step 8</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>통합</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Production 승격, Git rollback과 정리</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1. Registry stage를 Production으로 승인
-2. staging 종료 후 production Git 승격
-3. production OpenAI API 검증
-4. git revert로 이전 model URI rollback
-5. Week5 전용 Namespace/Application/Secret 정리</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>승격·롤백 증적과 원복된 클러스터</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>"승인·배포·롤백을 선언형 이력으로 운영하려면?"</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>RHOAI + OpenShift Pipelines/GitOps</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>🔶</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>🔶</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>기존 DSC/Registry/GPU Operator는 보존</t>
+    <row r="1" ht="17.25" customHeight="1" s="10">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>v0.9 → v1.1(설치·RawDeployment·홈랩 disconnected 보정) 변경점</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>v0.9 (동료)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>v1.1 (나)</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>이유</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>설치</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>없음 (기성 클러스터 전제)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Week1 Day1-2 설치 트랙 추가(빈 SNO)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>매니저 오더=딜리버리. '직접 구축·납품' 역량이 핵심</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="49.5" customHeight="1" s="10">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>기준 환경</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>airgap 미반영 + GPU 데모랩</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>홈랩 disconnected OCP 4.22(SNO+GPU worker+CPU worker) 기준, 공식 지원 범위 차이는 트러블슈팅 조건으로 명시</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>사용자 홈랩 실제 환경 반영. v1.0의 connected SNO 전제 보정</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="33" customHeight="1" s="10">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>서빙 모드</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Serverless 전제(canaryTrafficPercent)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>KServe RawDeployment. Service Mesh/Serverless/Authorino 기본 제외</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>RHOAI 3.4 공식 문서/릴리즈노트 기준 RawDeployment 중심. Serverless/ModelMesh 계열 제외</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="33" customHeight="1" s="10">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>멀티모델(ModelMesh)</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Day4 포함</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>ModelMesh는 3.x deprecated</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="33" customHeight="1" s="10">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>카나리</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Day3 canaryTrafficPercent</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>OpenShift Route alternateBackends/weight 기반 Blue-Green/A-B. Gateway API HTTPRoute는 GatewayClass/controller 준비 후 보강</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>KServe canaryTrafficPercent는 Serverless 전용으로 보고 RawDeployment 기본 실습에서 제외. Route weight는 OCP Route 공식 API로 검증 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>LLM 안전</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Rate Limiting만</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Guardrails/PII 세션 추가(Day13)</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>규제 금융/공공 고객 하드 요건</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="33" customHeight="1" s="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>계승(유지)</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>세션별 고객질문 / llm-d·GuideLLM / GPU 공유(Time-Slicing 중심, MIG 조건부) / AI500·AI267 매핑</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>동료 v0.9의 강점은 유지하되 현재 홈랩과 공식문서 기준으로 실행 가능성 보정</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="33" customHeight="1" s="10">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Pipeline 계보</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>KFP·Registry·서빙 실습이 일자별로 분리</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Day7 KFP artifact → Day8 S3 승격/Registry v1·v2/KServe → Day10 Route·GitOps가 같은 Run ID·SHA-256을 추적</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>모델 파일과 서빙 리소스가 다른 실습에서 섞이지 않도록 단일 lineage E2E로 보정</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="33" customHeight="1" s="10">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Kueue 운영</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>GPU 공유·부서별 cohort 중심 계획</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Red Hat build of Kueue Operator + DSC Unmanaged, team-cq/team-lq admission·priority·preemption. shared cohort 제외</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>RHOAI 3.4 지원 범위와 현재 홈랩에서 직접 검증한 구성에 맞춤</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="33" customHeight="1" s="10">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Models-as-a-Service</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>vLLM/llm-d 벤치마크 중심</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>RHCL·Gateway·PostgreSQL·LLMInferenceService·MaaSModelRef·Subscription/Auth/API key를 통한 MaaS 기능 검증</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>단순 vLLM 서빙이 아니라 RHOAI MaaS의 governance와 GA/TP 경계를 학습</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="33" customHeight="1" s="10">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>운영 검증</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Grafana/GuideLLM 등 계획형 항목 포함</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>UWM·ServiceMonitor·PromQL·PrometheusRule·Guardrails와 Pipeline/ISVC/Quota 장애 3종을 재현 가능한 CLI로 검증</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>미러·GPU·리소스 제약이 있는 홈랩에서도 반복 가능한 실습 결과를 우선</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="49.5" customHeight="1" s="10">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>2GPU Tensor Parallel</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>추가 Week6에서 같은 GPU worker의 RTX 5060 Ti 2장, KServe Standard vLLM TP1/TP2, NCCL rank와 PCIe 통신비를 비교</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>논리 GPU 공유와 물리 multi-GPU 병렬화를 구분하고, 작은 모델에서 TP가 반드시 빠르지 않다는 운영 판단까지 검증</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="75" customHeight="1" s="10">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>운영관리 보강</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>운영관리-보강 탭의 계획형 항목</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>추가 Week7에서 RHBK 26.6 OIDC, OADP 1.6 FSB, Ray/Kueue, PrometheusRule·audit, Kueue 장애, Dashboard customization, quota·Agent ISO를 재현 가능한 Step으로 구성</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>RHOAI 3.4/OCP 4.22 공식 API와 현재 platform=None 홈랩 조건에 맞춰 운영자 runbook으로 구체화</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
@@ -1418,25 +1182,24 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="7" customWidth="1" style="8" min="1" max="1"/>
-    <col width="8" customWidth="1" style="8" min="2" max="2"/>
-    <col width="26" customWidth="1" style="8" min="3" max="3"/>
-    <col width="46" customWidth="1" style="8" min="4" max="4"/>
-    <col width="26" customWidth="1" style="8" min="5" max="5"/>
-    <col width="34" customWidth="1" style="8" min="6" max="6"/>
-    <col width="16" customWidth="1" style="8" min="7" max="7"/>
-    <col width="7" customWidth="1" style="8" min="8" max="9"/>
-    <col width="30" customWidth="1" style="8" min="10" max="10"/>
+    <col width="7" customWidth="1" style="10" min="1" max="1"/>
+    <col width="8" customWidth="1" style="10" min="2" max="2"/>
+    <col width="26" customWidth="1" style="10" min="3" max="3"/>
+    <col width="46" customWidth="1" style="10" min="4" max="4"/>
+    <col width="26" customWidth="1" style="10" min="5" max="5"/>
+    <col width="34" customWidth="1" style="10" min="6" max="6"/>
+    <col width="16" customWidth="1" style="10" min="7" max="7"/>
+    <col width="7" customWidth="1" style="10" min="8" max="9"/>
+    <col width="30" customWidth="1" style="10" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" s="8">
-      <c r="A1" s="10" t="inlineStr">
+    <row r="1" ht="17.25" customHeight="1" s="10">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Week 1: 설치 + 기본 서빙 (홈랩 disconnected / SNO+workers) — "빈 클러스터에 RHOAI를 올리고 첫 모델을 RawDeployment로 서빙하라"</t>
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -1489,7 +1252,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="82.5" customHeight="1" s="8">
+    <row r="4" ht="82.5" customHeight="1" s="10">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Day 1</t>
@@ -1545,7 +1308,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="132" customHeight="1" s="8">
+    <row r="5" ht="132" customHeight="1" s="10">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Day 2</t>
@@ -1602,7 +1365,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="82.5" customHeight="1" s="8">
+    <row r="6" ht="82.5" customHeight="1" s="10">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Day 3</t>
@@ -1658,7 +1421,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="82.5" customHeight="1" s="8">
+    <row r="7" ht="82.5" customHeight="1" s="10">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Day 4</t>
@@ -1713,7 +1476,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="99" customHeight="1" s="8">
+    <row r="8" ht="99" customHeight="1" s="10">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Day 5</t>
@@ -1783,18 +1546,18 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="7" customWidth="1" style="8" min="1" max="1"/>
-    <col width="8" customWidth="1" style="8" min="2" max="2"/>
-    <col width="26" customWidth="1" style="8" min="3" max="3"/>
-    <col width="46" customWidth="1" style="8" min="4" max="4"/>
-    <col width="26" customWidth="1" style="8" min="5" max="5"/>
-    <col width="34" customWidth="1" style="8" min="6" max="6"/>
-    <col width="16" customWidth="1" style="8" min="7" max="7"/>
-    <col width="7" customWidth="1" style="8" min="8" max="9"/>
-    <col width="30" customWidth="1" style="8" min="10" max="10"/>
+    <col width="7" customWidth="1" style="10" min="1" max="1"/>
+    <col width="8" customWidth="1" style="10" min="2" max="2"/>
+    <col width="26" customWidth="1" style="10" min="3" max="3"/>
+    <col width="46" customWidth="1" style="10" min="4" max="4"/>
+    <col width="26" customWidth="1" style="10" min="5" max="5"/>
+    <col width="34" customWidth="1" style="10" min="6" max="6"/>
+    <col width="16" customWidth="1" style="10" min="7" max="7"/>
+    <col width="7" customWidth="1" style="10" min="8" max="9"/>
+    <col width="30" customWidth="1" style="10" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" s="8">
+    <row r="1" ht="17.25" customHeight="1" s="10">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Week 2: ML 학습 + 파이프라인 + 보안 (홈 SNO / CPU) — "직접 훈련하고 등록·배포·격리하라"</t>
@@ -1853,7 +1616,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="82.5" customHeight="1" s="8">
+    <row r="4" ht="82.5" customHeight="1" s="10">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Day 6</t>
@@ -1908,7 +1671,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="82.5" customHeight="1" s="8">
+    <row r="5" ht="82.5" customHeight="1" s="10">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Day 7</t>
@@ -1963,7 +1726,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="82.5" customHeight="1" s="8">
+    <row r="6" ht="82.5" customHeight="1" s="10">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Day 8</t>
@@ -2018,7 +1781,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="99" customHeight="1" s="8">
+    <row r="7" ht="99" customHeight="1" s="10">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Day 9</t>
@@ -2073,7 +1836,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="115.5" customHeight="1" s="8">
+    <row r="8" ht="115.5" customHeight="1" s="10">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Day 10</t>
@@ -2146,25 +1909,24 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="7" customWidth="1" style="8" min="1" max="1"/>
-    <col width="8" customWidth="1" style="8" min="2" max="2"/>
-    <col width="26" customWidth="1" style="8" min="3" max="3"/>
-    <col width="46" customWidth="1" style="8" min="4" max="4"/>
-    <col width="26" customWidth="1" style="8" min="5" max="5"/>
-    <col width="34" customWidth="1" style="8" min="6" max="6"/>
-    <col width="16" customWidth="1" style="8" min="7" max="7"/>
-    <col width="7" customWidth="1" style="8" min="8" max="9"/>
-    <col width="30" customWidth="1" style="8" min="10" max="10"/>
+    <col width="7" customWidth="1" style="10" min="1" max="1"/>
+    <col width="8" customWidth="1" style="10" min="2" max="2"/>
+    <col width="26" customWidth="1" style="10" min="3" max="3"/>
+    <col width="46" customWidth="1" style="10" min="4" max="4"/>
+    <col width="26" customWidth="1" style="10" min="5" max="5"/>
+    <col width="34" customWidth="1" style="10" min="6" max="6"/>
+    <col width="16" customWidth="1" style="10" min="7" max="7"/>
+    <col width="7" customWidth="1" style="10" min="8" max="9"/>
+    <col width="30" customWidth="1" style="10" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" s="8">
-      <c r="A1" s="10" t="inlineStr">
+    <row r="1" ht="17.25" customHeight="1" s="10">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Week 3: 모니터링 + MaaS + GPU (일부 GPU 랩) — "AI 워크로드를 운영하고 LLM을 서빙하라"</t>
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -2217,7 +1979,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="115.5" customHeight="1" s="8">
+    <row r="4" ht="115.5" customHeight="1" s="10">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Day 11</t>
@@ -2273,7 +2035,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="115.5" customHeight="1" s="8">
+    <row r="5" ht="115.5" customHeight="1" s="10">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Day 12</t>
@@ -2330,7 +2092,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="115.5" customHeight="1" s="8">
+    <row r="6" ht="115.5" customHeight="1" s="10">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Day 13</t>
@@ -2387,7 +2149,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="115.5" customHeight="1" s="8">
+    <row r="7" ht="115.5" customHeight="1" s="10">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Day 14</t>
@@ -2444,7 +2206,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="115.5" customHeight="1" s="8">
+    <row r="8" ht="115.5" customHeight="1" s="10">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Day 15</t>
@@ -2517,170 +2279,170 @@
   <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="26" customWidth="1" style="8" min="1" max="1"/>
-    <col width="28" customWidth="1" style="8" min="2" max="2"/>
-    <col width="14" customWidth="1" style="8" min="3" max="3"/>
-    <col width="70" customWidth="1" style="8" min="4" max="4"/>
+    <col width="26" customWidth="1" style="10" min="1" max="1"/>
+    <col width="14" customWidth="1" style="10" min="2" max="2"/>
+    <col width="50" customWidth="1" style="10" min="3" max="3"/>
+    <col width="40" customWidth="1" style="10" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" s="8">
+    <row r="1" ht="17.25" customHeight="1" s="10">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>환경 매핑 (홈랩 disconnected 기준 + GPU worker 사용)</t>
+          <t>컨설턴트 역량 매핑 (딜리버리 역량 추가)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>환경</t>
+          <t>역량</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>핸즈온 영역</t>
+          <t>관련 Week</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>사용 Day</t>
+          <t>핸즈온 세션</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>사용 컴포넌트</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="33" customHeight="1" s="8">
+          <t>고객 상황</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>홈랩 OCP 4.22 (SNO+workers, disconnected)</t>
+          <t>딜리버리/설치 (Delivery)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>설치 + 기본 서빙</t>
+          <t>Week 1</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Day 1-5</t>
+          <t>Day 1-2: 빈 SNO에 RHOAI 설치·DSC·RawDeployment</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>TrueNAS NFS CSI, TrueNAS S3 Data Connection, cert-manager, RHOAI Operator, DSCI/DSC v2, KServe RawDeployment, OpenShift Route alternateBackends/weight</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
+          <t>"폐쇄망에 RHOAI를 직접 구축·납품해 주세요."</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="33" customHeight="1" s="10">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>홈 SNO (CPU)</t>
+          <t>고객 상담 (Consultation)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>ML + 파이프라인 + 보안</t>
+          <t>Week 1-3</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Day 6-10</t>
+          <t>배포 가능여부/프레임워크/배포전략, ML 워크플로, GPU·MaaS·거버넌스</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Workbench, KFP, Model Registry, RBAC, Secret, ResourceQuota, (선택)Argo CD</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="33" customHeight="1" s="8">
+          <t>"저희 모델/LLM을 RHOAI에 올릴 수 있나요?"</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>홈 SNO (CPU)</t>
+          <t>PoC</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>모니터링·Guardrails (GPU 메트릭 제외)</t>
+          <t>Week 1,3</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Day 13 일부</t>
+          <t>Day 5 모델 온보딩 / Day 15 금융·제조 시나리오</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>UWM, Prometheus, Grafana, TrustyAI/Guardrails</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="33" customHeight="1" s="8">
+          <t>"PoC로 모델 3개를 1주 안에 배포해보세요."</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="33" customHeight="1" s="10">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>홈랩 GPU worker</t>
+          <t>장애 대응 (Troubleshooting)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>GPU enablement·공유</t>
+          <t>Week 1-3</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Day 11-12</t>
+          <t>Day 3 상태·로그·이벤트 / Day 7 파이프라인 / Day 15 장애 3종</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>NFD, NVIDIA GPU Operator, KMM, HardwareProfile, Time-Slicing. MIG는 지원 GPU 랩에서만</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="33" customHeight="1" s="8">
+          <t>"모델이 배포 안 됩니다. 왜죠?"</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="33" customHeight="1" s="10">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>홈랩 GPU worker / 보강 GPU 랩</t>
+          <t>기술 교육 (Education)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>MaaS + llm-d</t>
+          <t>Week 1-3</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Day 14</t>
+          <t>전체 세션 직접 경험 후 고객 교육</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>vLLM, ServingRuntime, OpenAI 호환 API, GuideLLM. llm-d/LWS/RateLimit 고급 실습은 카탈로그 추가 후</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>"고객 DevOps 팀에 RHOAI를 교육해야 합니다."</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="33" customHeight="1" s="10">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>프로젝트 지원 (Project Support)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>Week 1-3</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Day 15</t>
+          <t>설치 아키텍처·MLOps 체계·엔터프라이즈 설계</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>전체 컴포넌트 연동 + 고객 시나리오</t>
+          <t>"엔터프라이즈 AI 플랫폼을 설계·구축해주세요."</t>
         </is>
       </c>
     </row>
@@ -2696,177 +2458,469 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="26" customWidth="1" style="8" min="1" max="1"/>
-    <col width="14" customWidth="1" style="8" min="2" max="2"/>
-    <col width="50" customWidth="1" style="8" min="3" max="3"/>
-    <col width="40" customWidth="1" style="8" min="4" max="4"/>
+    <col width="8" customWidth="1" style="10" min="1" max="1"/>
+    <col width="9" customWidth="1" style="10" min="2" max="2"/>
+    <col width="30" customWidth="1" style="10" min="3" max="3"/>
+    <col width="64" customWidth="1" style="10" min="4" max="4"/>
+    <col width="26" customWidth="1" style="10" min="5" max="5"/>
+    <col width="28" customWidth="1" style="10" min="6" max="6"/>
+    <col width="16" customWidth="1" style="10" min="7" max="7"/>
+    <col width="7" customWidth="1" style="10" min="8" max="9"/>
+    <col width="40" customWidth="1" style="10" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" s="8">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>컨설턴트 역량 매핑 (딜리버리 역량 추가)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>역량</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>관련 Week</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>핸즈온 세션</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>고객 상황</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>딜리버리/설치 (Delivery)</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Week 1</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Day 1-2: 빈 SNO에 RHOAI 설치·DSC·RawDeployment</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>"폐쇄망에 RHOAI를 직접 구축·납품해 주세요."</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="33" customHeight="1" s="8">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>고객 상담 (Consultation)</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Week 1-3</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>배포 가능여부/프레임워크/배포전략, ML 워크플로, GPU·MaaS·거버넌스</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>"저희 모델/LLM을 RHOAI에 올릴 수 있나요?"</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>PoC</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Week 1,3</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Day 5 모델 온보딩 / Day 15 금융·제조 시나리오</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>"PoC로 모델 3개를 1주 안에 배포해보세요."</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="33" customHeight="1" s="8">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>장애 대응 (Troubleshooting)</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Week 1-3</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Day 3 상태·로그·이벤트 / Day 7 파이프라인 / Day 15 장애 3종</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>"모델이 배포 안 됩니다. 왜죠?"</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="33" customHeight="1" s="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>기술 교육 (Education)</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Week 1-3</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>전체 세션 직접 경험 후 고객 교육</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>"고객 DevOps 팀에 RHOAI를 교육해야 합니다."</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="33" customHeight="1" s="8">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>프로젝트 지원 (Project Support)</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Week 1-3</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>설치 아키텍처·MLOps 체계·엔터프라이즈 설계</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>"엔터프라이즈 AI 플랫폼을 설계·구축해주세요."</t>
+    <row r="1" ht="30" customHeight="1" s="10">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>추가 스터디 — GPU 공유(Time-Slicing+MPS) × Kueue Cohort 빌림/회수/부분격리 : "쪼갠 GPU를 부서별로 빌려쓰고 · 회수하고 · 일부는 전유시켜라"</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20.1" customHeight="1" s="10">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>세션명</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>수행할 작업 (Hands-on)</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>예상 결과물</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>고객 상황 연결</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>환경</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>AI500</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>AI267</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="150" customHeight="1" s="10">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>사전</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>사전점검</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>GPU 공유 타당성 + 혼합전략 검증</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1. 5060 Ti = MIG 불가 → Time-Slicing/MPS만 가능 확인
+2. ⚠️ 단일 SNO에서 GPU0=Time-Slice / GPU1=MPS "혼합"이 device-plugin에서 되는지 검증 (sharing config는 보통 노드/리소스 단위 → GPU별 다른 전략은 비표준)
+3. 안 되면 fallback: (a) 둘 다 Time-Slice ×2(=4) (b) 노드 라벨 nvidia.com/device-plugin.config로 전략 분리</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>타당성 판단 + 분할 전략 확정</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>"한정된 GPU를 부서별로 어떻게 나눠 쓰나?"</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>홈 SNO (5060 Ti ×2)</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>cohort는 Kueue 개념 → 카드 무관(GPU가 cohort를 "지원"하는 게 아님). 전제=Time-Slice/MPS 동작(컨슈머 OK, MIG만 불가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="150" customHeight="1" s="10">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Step 1</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>핸즈온</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>GPU 분할: Time-Slicing ×2 + MPS ×2 → nvidia.com/gpu 4 광고</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1. NVIDIA device-plugin sharing ConfigMap: GPU0 timeSlicing replicas=2
+2. GPU1 MPS replicas=2 (가능 시 노드 라벨로 config 분리)
+3. node allocatable nvidia.com/gpu = 4 확인 (kubectl describe node)
+4. nvidia-smi 파드로 분할 동작 확인</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>nvidia.com/gpu: 4 (2 TS + 2 MPS)</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>"GPU 한 장을 여러 워크로드가 나눠 쓰게 하려면?"</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>홈 SNO (GPU 랩)</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>광고 이름이 전부 nvidia.com/gpu(동일) → 같은 이름이라 cohort 빌림 대상. AI500 모듈92 Time-Slicing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="150" customHeight="1" s="10">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Step 2</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>핸즈온</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Kueue: ClusterQueue 2개 + 동일 cohort + LocalQueue</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1. ResourceFlavor(gpu-flavor, nodeLabels)
+2. team-a-cq: nominalQuota nvidia.com/gpu=2, cohort=research, preemption.reclaimWithinCohort=Any
+3. team-b-cq: gpu=2, cohort=research, reclaim=Any
+4. ns-a/ns-b에 LocalQueue(clusterQueue 지정)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>cohort research 총 4 (2+2), 보장 각 2</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>"부서 A/B에 GPU를 보장하되 남으면 공유하려면?"</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>홈 SNO (Kueue 로직)</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Kueue 로직 자체는 CPU로도 학습 가능하나 여기선 분할 GPU로 검증</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="150" customHeight="1" s="10">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Step 3</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>핸즈온</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>빌림 검증: A가 4 요청 → B 유휴분 2 빌림</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1. B 유휴 상태에서 ns-a에 gpu 4개 요구 Job 제출
+2. A = 자기 2 + cohort 2 빌려 4개 admit 확인 (kubectl get workloads; ClusterQueue status의 borrowed)
+3. 실제 파드 배치/nvidia-smi로 점유 확인</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>A가 4개 동시 admit(2 빌림) 관찰</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>"놀고 있는 다른 부서 GPU를 끌어다 쓰게?"</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>홈 SNO (GPU 랩)</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>⚠️ TS/MPS는 시분할 공유 → 빌린 단위는 격리 실자원 아님(경합). 장부상 빌림만 검증</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="150" customHeight="1" s="10">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Step 4</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>핸즈온</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>회수(reclaim) 검증: B가 2 요청 → A 빌린 워크로드 선점</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1. ns-b에 gpu 2 요구 Job 제출
+2. reclaimWithinCohort로 A의 빌린 2개 preempt 확인(workload 이벤트/상태)
+3. B 보장 2 회수, A는 2로 축소 확인</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>빌림→회수 사이클 관찰, 보장(nominalQuota) 유지 입증</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>"공유하다가 주인이 쓰겠다면 돌려받게?"</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>홈 SNO (GPU 랩)</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>reclaimWithinCohort 없으면 회수 안 됨(필수 설정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="150" customHeight="1" s="10">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Step 5</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>핸즈온</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>부분 격리: 4단위 중 일부(각 CQ 1씩)를 cohort 제외(전유)</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>목표: TS 1 + MPS 1은 빌림 금지(부서 전유), 나머지 TS 1 + MPS 1만 공유.
+▶ 방법A (수량 기반, SNO 현실적): 각 ClusterQueue에 lendingLimit=1
+   → 보장 2 중 1만 빌려주고 1은 전유. A가 4 요청 시 자기2+빌림1=3만 admit, B 전유1은 안 빌려짐 확인.
+▶ 방법B (메커니즘 구분, 고급/타당성 검증): device-plugin renameByDefault로
+   TS→nvidia.com/gpu.shared-ts / MPS→...-mps 등 "다른 리소스명" 부여 →
+   공유용 flavor만 cohort, 전유용은 lendingLimit=0(또는 cohort 밖).
+⚠️ 단일 노드에서 TS/MPS가 같은 nvidia.com/gpu로 광고되면 Kueue가 둘을 "구분 못 함"
+   → 메커니즘별 구분은 "리소스명 분리(rename)" 또는 노드/라벨 분리가 전제. SNO 동일명이면 방법A(수량)만 현실적.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>부분 공유(2 공유 + 2 전유) 동작 + "전유분은 안 빌려짐" 검증</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>"일부 GPU는 부서 전용 보장, 나머지만 공유하고 싶어요"</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>홈 SNO (GPU 랩)</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>lendingLimit=수량 예약 / rename=메커니즘·단위 구분. Kueue는 단위를 수량으로 다루지 "MPS/TS 어느 물리단위"로 못 집음</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="150" customHeight="1" s="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Step 6</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>통합</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>대조: without shared cohort(완전 격리) + with/without 비교 정리</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1. cohort 제거(또는 cohort명 분리)로 완전 격리
+2. A가 4 요청해도 2만 실행, B 유휴여도 못 빌림 확인
+3. with / 부분격리(Step5) / without 3가지 활용률·보장 비교표 작성
+4. (선택) borrowingLimit 실험으로 빌림 상한도 비교</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3구성(공유/부분격리/완전격리) 비교 + 멀티테넌트 배분 제안자료</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>"격리 보장 vs 효율 공유 — 고객에 뭘 권하나?"</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>홈 SNO</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Red Hat 문서 "NVIDIA GPUs without shared cohort"가 이 완전격리 구성(= GPU가 cohort 미지원이 아니라, 빌림 없이 쓰는 설정)</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:J1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
@@ -2878,288 +2932,580 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="18" customWidth="1" style="8" min="1" max="1"/>
-    <col width="34" customWidth="1" style="8" min="2" max="2"/>
-    <col width="40" customWidth="1" style="8" min="3" max="3"/>
-    <col width="46" customWidth="1" style="8" min="4" max="4"/>
+    <col width="8" customWidth="1" style="10" min="1" max="1"/>
+    <col width="9" customWidth="1" style="10" min="2" max="2"/>
+    <col width="30" customWidth="1" style="10" min="3" max="3"/>
+    <col width="64" customWidth="1" style="10" min="4" max="4"/>
+    <col width="26" customWidth="1" style="10" min="5" max="5"/>
+    <col width="28" customWidth="1" style="10" min="6" max="6"/>
+    <col width="16" customWidth="1" style="10" min="7" max="7"/>
+    <col width="7" customWidth="1" style="10" min="8" max="9"/>
+    <col width="40" customWidth="1" style="10" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" s="8">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>v0.9 → v1.1(설치·RawDeployment·홈랩 disconnected 보정) 변경점</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>v0.9 (동료)</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>v1.1 (나)</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>이유</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>설치</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>없음 (기성 클러스터 전제)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Week1 Day1-2 설치 트랙 추가(빈 SNO)</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>매니저 오더=딜리버리. '직접 구축·납품' 역량이 핵심</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="49.5" customHeight="1" s="8">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>기준 환경</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>airgap 미반영 + GPU 데모랩</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>홈랩 disconnected OCP 4.22(SNO+GPU worker+CPU worker) 기준, 공식 지원 범위 차이는 트러블슈팅 조건으로 명시</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>사용자 홈랩 실제 환경 반영. v1.0의 connected SNO 전제 보정</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="33" customHeight="1" s="8">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>서빙 모드</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Serverless 전제(canaryTrafficPercent)</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>KServe RawDeployment. Service Mesh/Serverless/Authorino 기본 제외</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>RHOAI 3.4 공식 문서/릴리즈노트 기준 RawDeployment 중심. Serverless/ModelMesh 계열 제외</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="33" customHeight="1" s="8">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>멀티모델(ModelMesh)</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Day4 포함</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>ModelMesh는 3.x deprecated</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="33" customHeight="1" s="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>카나리</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Day3 canaryTrafficPercent</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>OpenShift Route alternateBackends/weight 기반 Blue-Green/A-B. Gateway API HTTPRoute는 GatewayClass/controller 준비 후 보강</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>KServe canaryTrafficPercent는 Serverless 전용으로 보고 RawDeployment 기본 실습에서 제외. Route weight는 OCP Route 공식 API로 검증 가능</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>LLM 안전</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Rate Limiting만</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Guardrails/PII 세션 추가(Day13)</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>규제 금융/공공 고객 하드 요건</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="33" customHeight="1" s="8">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>계승(유지)</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>세션별 고객질문 / llm-d·GuideLLM / GPU 공유(Time-Slicing 중심, MIG 조건부) / AI500·AI267 매핑</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>동료 v0.9의 강점은 유지하되 현재 홈랩과 공식문서 기준으로 실행 가능성 보정</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="33" customHeight="1" s="8">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Pipeline 계보</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>KFP·Registry·서빙 실습이 일자별로 분리</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Day7 KFP artifact → Day8 S3 승격/Registry v1·v2/KServe → Day10 Route·GitOps가 같은 Run ID·SHA-256을 추적</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>모델 파일과 서빙 리소스가 다른 실습에서 섞이지 않도록 단일 lineage E2E로 보정</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="33" customHeight="1" s="8">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Kueue 운영</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>GPU 공유·부서별 cohort 중심 계획</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Red Hat build of Kueue Operator + DSC Unmanaged, team-cq/team-lq admission·priority·preemption. shared cohort 제외</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>RHOAI 3.4 지원 범위와 현재 홈랩에서 직접 검증한 구성에 맞춤</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="33" customHeight="1" s="8">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Models-as-a-Service</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>vLLM/llm-d 벤치마크 중심</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>RHCL·Gateway·PostgreSQL·LLMInferenceService·MaaSModelRef·Subscription/Auth/API key를 통한 MaaS 기능 검증</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>단순 vLLM 서빙이 아니라 RHOAI MaaS의 governance와 GA/TP 경계를 학습</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="33" customHeight="1" s="8">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>운영 검증</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Grafana/GuideLLM 등 계획형 항목 포함</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>UWM·ServiceMonitor·PromQL·PrometheusRule·Guardrails와 Pipeline/ISVC/Quota 장애 3종을 재현 가능한 CLI로 검증</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>미러·GPU·리소스 제약이 있는 홈랩에서도 반복 가능한 실습 결과를 우선</t>
+    <row r="1" ht="30" customHeight="1" s="10">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>추가 스터디 — Tekton CI × KFP × Trainer v2 × Model Registry × Argo CD × KServe vLLM : "LLM을 훈련하고 검증해 Git으로 승격·롤백하라"</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20.1" customHeight="1" s="10">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>세션명</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>수행할 작업 (Hands-on)</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>예상 결과물</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>고객 상황 연결</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>환경</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>AI500</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>AI267</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="150" customHeight="1" s="10">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>사전</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>사전점검</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>LLM MLOps 운영 경계와 지원 범위 확인</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1. Tekton=CI, KFP=ML workflow, Trainer v2=GPU 학습, Argo CD=CD 역할 분리
+2. RHOAI/Trainer/KFP/KServe/GitOps API와 GPU 확인
+3. 단일 GPU에서 학습→staging→production 순차 실행 계획
+4. MaaS-vLLM TP는 운영 기본 경로에서 제외</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>지원 범위·아키텍처·검증 순서 확정</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>"LLM 학습부터 운영 배포까지 책임 경계를 어떻게 나누나?"</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>홈 OCP + GPU worker + S3/Gitea/Nexus</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>RHOAI 3.4 기준. KServe Standard vLLM 경로</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="150" customHeight="1" s="10">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Step 1</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>핸즈온</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>폐쇄망 LLM artifact 준비</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1. boto3와 전이 wheel을 Nexus hosted에 반입
+2. Qwen2.5 0.5B ModelCar에서 base model 추출
+3. base model과 24건 합성 SFT JSONL을 S3에 버전 고정
+4. digest와 object metadata 기록</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>재현 가능한 base model·dataset·Python wheel</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>"인터넷 없는 환경에서 모델과 패키지를 어떻게 재현하나?"</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Bastion + 5010 model registry + Nexus + S3</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>실제 ID/PW는 문서·Git에 기록 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="150" customHeight="1" s="10">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Step 2</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>핸즈온</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>OpenShift Pipelines와 프로젝트 구성</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1. OpenShift Pipelines Operator 설치
+2. CI/학습, staging, production Namespace와 최소 RBAC 구성
+3. S3·registry·Gitea Secret을 명령으로 생성
+4. Kubernetes-native pipelineStore DSPA 생성</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Tekton/KFP/Trainer/serving 실행 기반</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>"CI와 환경별 배포 권한을 어떻게 분리하나?"</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>OCP cluster-admin + RHOAI</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Secret manifest는 공개 저장소에 두지 않음</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="150" customHeight="1" s="10">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Step 3</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>핸즈온</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Source와 GitOps 저장소 분리</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1. source repo에 코드·dataset·Containerfile·KFP DSL 작성
+2. GitOps repo에 pipelines/staging/production 구조 작성
+3. ServingRuntime만 초기 desired state로 등록
+4. 두 repo 기밀 검사 후 push</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>소스 저장소와 배포 선언 저장소</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>"애플리케이션 코드와 운영 선언을 왜 분리하나?"</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Gitea + Bastion</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Tekton은 GitOps repo만 변경하고 ISVC 직접 적용 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="150" customHeight="1" s="10">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Step 4</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>핸즈온</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Tekton CI와 Argo CD 연결</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1. Argo CD private repository Secret과 Application 3개 생성
+2. Tekton CI/promotion Pipeline과 EventListener 생성
+3. 수동 PipelineRun으로 단계별 검증
+4. Gitea main push webhook 연결</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>push→CI→GitOps 동기화 경로</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>"코드 push를 검증·빌드·배포 선언으로 연결하려면?"</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>OpenShift Pipelines + GitOps + Gitea</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Generic Gitea webhook은 랩용. 운영은 서명 검증 필수</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="150" customHeight="1" s="10">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Step 5</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>핸즈온</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Image digest와 Kubernetes-native KFP 추적</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1. source commit과 training image digest 확인
+2. KFP CR compile 결과를 GitOps repo에 발행
+3. Argo CD가 Pipeline/PipelineVersion 동기화
+4. DSPA API에 Run 자동 생성</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>commit→image→PipelineVersion→Run 추적성</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>"어떤 코드와 이미지로 학습했는지 감사 가능하게 하려면?"</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Tekton + Argo CD + RHOAI AI Pipelines</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Tekton Pipeline과 KFP Pipeline은 API와 역할이 다름</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="150" customHeight="1" s="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Step 6</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>핸즈온</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Trainer v2 LoRA 학습과 Registry 등록</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1. KFP component가 단일 GPU TrainJob 생성
+2. LoRA 학습 후 merged model/adapter/metrics를 S3에 저장
+3. KFP scalar metrics와 S3 metrics 비교
+4. Model Registry에 stage=Staging version 자동 등록</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>TrainJob·모델 산출물·지표·Registry version</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>"학습 결과와 지표, 소스 commit을 하나의 모델 버전으로 묶으려면?"</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>GPU worker + Trainer v2 + S3 + Model Registry</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>작은 합성 dataset은 경로 검증용이며 품질 기준 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="150" customHeight="1" s="10">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Step 7</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>핸즈온</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Staging gate와 KServe vLLM 검증</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1. Registry Staging과 train_loss gate 확인
+2. Tekton이 staging Git 선언 갱신
+3. Argo CD가 KServe Standard ISVC 배포
+4. OpenAI chat completions 호출과 추적정보 확인
+5. 실패 gate에서 Git 미변경 확인</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>승인 gate를 통과한 staging vLLM endpoint</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>"검증되지 않은 모델의 배포를 어떻게 차단하나?"</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Tekton + Argo CD + KServe + GPU</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>단일 GPU이므로 학습 종료 후 서빙</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="150" customHeight="1" s="10">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Step 8</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>통합</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Production 승격, Git rollback과 정리</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1. Registry stage를 Production으로 승인
+2. staging 종료 후 production Git 승격
+3. production OpenAI API 검증
+4. git revert로 이전 model URI rollback
+5. Week5 전용 Namespace/Application/Secret 정리</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>승격·롤백 증적과 원복된 클러스터</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>"승인·배포·롤백을 선언형 이력으로 운영하려면?"</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>RHOAI + OpenShift Pipelines/GitOps</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>기존 DSC/Registry/GPU Operator는 보존</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:J1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
@@ -3171,28 +3517,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="8" customWidth="1" style="8" min="1" max="1"/>
-    <col width="9" customWidth="1" style="8" min="2" max="2"/>
-    <col width="30" customWidth="1" style="8" min="3" max="3"/>
-    <col width="64" customWidth="1" style="8" min="4" max="4"/>
-    <col width="26" customWidth="1" style="8" min="5" max="5"/>
-    <col width="28" customWidth="1" style="8" min="6" max="6"/>
-    <col width="16" customWidth="1" style="8" min="7" max="7"/>
-    <col width="7" customWidth="1" style="8" min="8" max="9"/>
-    <col width="40" customWidth="1" style="8" min="10" max="10"/>
+    <col width="8" customWidth="1" style="10" min="1" max="1"/>
+    <col width="9" customWidth="1" style="10" min="2" max="2"/>
+    <col width="30" customWidth="1" style="10" min="3" max="3"/>
+    <col width="64" customWidth="1" style="10" min="4" max="4"/>
+    <col width="26" customWidth="1" style="10" min="5" max="5"/>
+    <col width="28" customWidth="1" style="10" min="6" max="6"/>
+    <col width="16" customWidth="1" style="10" min="7" max="7"/>
+    <col width="7" customWidth="1" style="10" min="8" max="9"/>
+    <col width="40" customWidth="1" style="10" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="8">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>추가 스터디 — GPU 공유(Time-Slicing+MPS) × Kueue Cohort 빌림/회수/부분격리 : "쪼갠 GPU를 부서별로 빌려쓰고 · 회수하고 · 일부는 전유시켜라"</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20.1" customHeight="1" s="8">
+    <row r="1" ht="30" customHeight="1" s="10">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>추가 스터디 — 2× RTX 5060 Ti 단일 노드 vLLM Tensor Parallel : "두 물리 GPU에 모델 tensor를 분할하고 통신 비용까지 검증하라"</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20.1" customHeight="1" s="10">
       <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Day</t>
@@ -3244,7 +3590,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="150" customHeight="1" s="8">
+    <row r="4" ht="150" customHeight="1" s="10">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>사전</t>
@@ -3257,34 +3603,36 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>GPU 공유 타당성 + 혼합전략 검증</t>
+          <t>두 번째 GPU passthrough와 exclusive GPU 2개 검증</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1. 5060 Ti = MIG 불가 → Time-Slicing/MPS만 가능 확인
-2. ⚠️ 단일 SNO에서 GPU0=Time-Slice / GPU1=MPS "혼합"이 device-plugin에서 되는지 검증 (sharing config는 보통 노드/리소스 단위 → GPU별 다른 전략은 비표준)
-3. 안 되면 fallback: (a) 둘 다 Time-Slice ×2(=4) (b) 노드 라벨 nvidia.com/device-plugin.config로 전략 분리</t>
+          <t>1. Proxmox VM 102에 두 번째 5060 Ti passthrough
+2. worker Ready와 NFD/GFD label 확인
+3. Device Plugin 공유 config/label이 null·absent인지 확인
+4. inventory Job이 nvidia.com/gpu=2를 할당받아 nvidia-smi -L/topo 출력</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>타당성 판단 + 분할 전략 확정</t>
+          <t>동일 worker의 물리 GPU capacity/allocatable 2/2와 PCIe topology</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>"한정된 GPU를 부서별로 어떻게 나눠 쓰나?"</t>
+          <t>한 노드의 여러 GPU를 실제 모델 추론에 함께 사용할 수 있는가?</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>홈 SNO (5060 Ti ×2)</t>
+          <t>홈 OCP GPU worker
+RTX 5060 Ti ×2</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>🔶</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -3294,11 +3642,11 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>cohort는 Kueue 개념 → 카드 무관(GPU가 cohort를 "지원"하는 게 아님). 전제=Time-Slice/MPS 동작(컨슈머 OK, MIG만 불가)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="150" customHeight="1" s="8">
+          <t>Time-Slicing slot 2개가 아니라 exclusive 물리 GPU 2개가 필요. 단일 노드 경로</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="150" customHeight="1" s="10">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Step 1</t>
@@ -3306,330 +3654,220 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>핸즈온/운영</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>TP 검증용 저자원 프로파일과 OCI 연결</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1. GPU worker request와 TP2 request 합산
+2. 필요 시 Dashboard component만 백업 후 Removed
+3. KServe/GPU Operator/DCGM 필수 구성 보존
+4. 5010 OCI ModelCar pull Secret 생성</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>TP2 scheduling headroom과 private ModelCar pull 경로</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>저사양 검증 클러스터에서 어떤 operand를 잠시 내려야 하는가?</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>홈 OCP + 5010 model registry</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>현재 자원에서는 제거 없이도 가능. Dashboard 제거는 선택이며 원복 필수</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="150" customHeight="1" s="10">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Step 2</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>핸즈온</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>GPU 분할: Time-Slicing ×2 + MPS ×2 → nvidia.com/gpu 4 광고</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1. NVIDIA device-plugin sharing ConfigMap: GPU0 timeSlicing replicas=2
-2. GPU1 MPS replicas=2 (가능 시 노드 라벨로 config 분리)
-3. node allocatable nvidia.com/gpu = 4 확인 (kubectl describe node)
-4. nvidia-smi 파드로 분할 동작 확인</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>nvidia.com/gpu: 4 (2 TS + 2 MPS)</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>"GPU 한 장을 여러 워크로드가 나눠 쓰게 하려면?"</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>홈 SNO (GPU 랩)</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>vLLM TP1 기준선</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1. Qwen2.5 0.5B ModelCar를 KServe Standard TP1로 배포
+2. Ready까지 시간과 GPU memory 기록
+3. OpenAI chat completion 동일 요청 5회 실행
+4. cold/warm TTFB와 total time 저장</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>GPU 1장 기준 startup·지연·VRAM 측정값</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>병렬화 효과를 판단할 단일 GPU 기준선을 어떻게 만드는가?</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>GPU worker + KServe Standard</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>광고 이름이 전부 nvidia.com/gpu(동일) → 같은 이름이라 cohort 빌림 대상. AI500 모듈92 Time-Slicing</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="150" customHeight="1" s="8">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Step 2</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>작은 모델은 TP1이 더 빠를 수 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="150" customHeight="1" s="10">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Step 3</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>핸즈온</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Kueue: ClusterQueue 2개 + 동일 cohort + LocalQueue</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1. ResourceFlavor(gpu-flavor, nodeLabels)
-2. team-a-cq: nominalQuota nvidia.com/gpu=2, cohort=research, preemption.reclaimWithinCohort=Any
-3. team-b-cq: gpu=2, cohort=research, reclaim=Any
-4. ns-a/ns-b에 LocalQueue(clusterQueue 지정)</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>cohort research 총 4 (2+2), 보장 각 2</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>"부서 A/B에 GPU를 보장하되 남으면 공유하려면?"</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>홈 SNO (Kueue 로직)</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>vLLM TP2와 NCCL rank 검증</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1. TP1 삭제 후 GPU 반환
+2. distributed-executor-backend=mp, tensor-parallel-size=2 배포
+3. GPU request=2, world size/rank/NCCL 로그 확인
+4. 두 GPU process·VRAM과 동일 요청 5회 측정</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>두 물리 GPU의 TP rank 0/1과 OpenAI API 성공</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>NVLink 없는 PCIe GPU 두 장에서도 Tensor Parallel이 동작하는가?</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>GPU worker RTX 5060 Ti ×2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Kueue 로직 자체는 CPU로도 학습 가능하나 여기선 분할 GPU로 검증</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="150" customHeight="1" s="8">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Step 3</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>핸즈온</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>빌림 검증: A가 4 요청 → B 유휴분 2 빌림</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1. B 유휴 상태에서 ns-a에 gpu 4개 요구 Job 제출
-2. A = 자기 2 + cohort 2 빌려 4개 admit 확인 (kubectl get workloads; ClusterQueue status의 borrowed)
-3. 실제 파드 배치/nvidia-smi로 점유 확인</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>A가 4개 동시 admit(2 빌림) 관찰</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>"놀고 있는 다른 부서 GPU를 끌어다 쓰게?"</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>홈 SNO (GPU 랩)</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>기능 합격 기준은 속도 향상이 아니라 두 rank·두 GPU·API 성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="150" customHeight="1" s="10">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Step 4</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>통합</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>TP1/TP2 비교, 해석과 원복</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1. warm TTFB/total, startup, GPU별 memory 비교
+2. PCIe/NCCL 통신비와 TP 적용 조건 해석
+3. ISVC/Runtime/Namespace와 port-forward 정리
+4. Dashboard 원상복구, 두 번째 GPU 유지 또는 선택 해제</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>TP 적용 판단표와 원복된 DSC/클러스터</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>더 많은 GPU가 항상 더 빠른가? 어떤 모델에 TP를 적용해야 하는가?</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>홈 OCP</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>⚠️ TS/MPS는 시분할 공유 → 빌린 단위는 격리 실자원 아님(경합). 장부상 빌림만 검증</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="150" customHeight="1" s="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Step 4</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>핸즈온</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>회수(reclaim) 검증: B가 2 요청 → A 빌린 워크로드 선점</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1. ns-b에 gpu 2 요구 Job 제출
-2. reclaimWithinCohort로 A의 빌린 2개 preempt 확인(workload 이벤트/상태)
-3. B 보장 2 회수, A는 2로 축소 확인</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>빌림→회수 사이클 관찰, 보장(nominalQuota) 유지 입증</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>"공유하다가 주인이 쓰겠다면 돌려받게?"</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>홈 SNO (GPU 랩)</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>🔶</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>reclaimWithinCohort 없으면 회수 안 됨(필수 설정)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="150" customHeight="1" s="8">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Step 5</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>핸즈온</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>부분 격리: 4단위 중 일부(각 CQ 1씩)를 cohort 제외(전유)</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>목표: TS 1 + MPS 1은 빌림 금지(부서 전유), 나머지 TS 1 + MPS 1만 공유.
-▶ 방법A (수량 기반, SNO 현실적): 각 ClusterQueue에 lendingLimit=1
-   → 보장 2 중 1만 빌려주고 1은 전유. A가 4 요청 시 자기2+빌림1=3만 admit, B 전유1은 안 빌려짐 확인.
-▶ 방법B (메커니즘 구분, 고급/타당성 검증): device-plugin renameByDefault로
-   TS→nvidia.com/gpu.shared-ts / MPS→...-mps 등 "다른 리소스명" 부여 →
-   공유용 flavor만 cohort, 전유용은 lendingLimit=0(또는 cohort 밖).
-⚠️ 단일 노드에서 TS/MPS가 같은 nvidia.com/gpu로 광고되면 Kueue가 둘을 "구분 못 함"
-   → 메커니즘별 구분은 "리소스명 분리(rename)" 또는 노드/라벨 분리가 전제. SNO 동일명이면 방법A(수량)만 현실적.</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>부분 공유(2 공유 + 2 전유) 동작 + "전유분은 안 빌려짐" 검증</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>"일부 GPU는 부서 전용 보장, 나머지만 공유하고 싶어요"</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>홈 SNO (GPU 랩)</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>🔶</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>lendingLimit=수량 예약 / rename=메커니즘·단위 구분. Kueue는 단위를 수량으로 다루지 "MPS/TS 어느 물리단위"로 못 집음</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="150" customHeight="1" s="8">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Step 6</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>통합</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>대조: without shared cohort(완전 격리) + with/without 비교 정리</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1. cohort 제거(또는 cohort명 분리)로 완전 격리
-2. A가 4 요청해도 2만 실행, B 유휴여도 못 빌림 확인
-3. with / 부분격리(Step5) / without 3가지 활용률·보장 비교표 작성
-4. (선택) borrowingLimit 실험으로 빌림 상한도 비교</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3구성(공유/부분격리/완전격리) 비교 + 멀티테넌트 배분 제안자료</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>"격리 보장 vs 효율 공유 — 고객에 뭘 권하나?"</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>홈 SNO</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>🔶</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>Red Hat 문서 "NVIDIA GPUs without shared cohort"가 이 완전격리 구성(= GPU가 cohort 미지원이 아니라, 빌림 없이 쓰는 설정)</t>
-        </is>
-      </c>
-    </row>
+          <t>KServe Standard 단일 노드 TP. multi-node LLMInferenceService/llm-d 범위 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="150" customHeight="1" s="10"/>
+    <row r="10" ht="150" customHeight="1" s="10"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
@@ -3648,25 +3886,25 @@
   <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="8" customWidth="1" style="8" min="1" max="1"/>
-    <col width="11" customWidth="1" style="8" min="2" max="2"/>
-    <col width="32" customWidth="1" style="8" min="3" max="3"/>
-    <col width="64" customWidth="1" style="8" min="4" max="4"/>
-    <col width="26" customWidth="1" style="8" min="5" max="5"/>
-    <col width="30" customWidth="1" style="8" min="6" max="6"/>
-    <col width="16" customWidth="1" style="8" min="7" max="7"/>
-    <col width="7" customWidth="1" style="8" min="8" max="9"/>
-    <col width="42" customWidth="1" style="8" min="10" max="10"/>
+    <col width="8" customWidth="1" style="10" min="1" max="1"/>
+    <col width="11" customWidth="1" style="10" min="2" max="2"/>
+    <col width="32" customWidth="1" style="10" min="3" max="3"/>
+    <col width="64" customWidth="1" style="10" min="4" max="4"/>
+    <col width="26" customWidth="1" style="10" min="5" max="5"/>
+    <col width="30" customWidth="1" style="10" min="6" max="6"/>
+    <col width="16" customWidth="1" style="10" min="7" max="7"/>
+    <col width="7" customWidth="1" style="10" min="8" max="9"/>
+    <col width="42" customWidth="1" style="10" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="8">
+    <row r="1" ht="30" customHeight="1" s="10">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>운영·관리 보강 — Managing OpenShift AI 3.4 가이드 갭(admin/딜리버리) : "관리자가 RHOAI를 인증·백업·분산·관측·커스터마이즈하라" (행=중요도순)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20.1" customHeight="1" s="8">
+          <t>Week 7: 운영·관리 보강 — RHOAI/OCP 관리자가 인증·백업·분산·관측·커스터마이징·용량을 운영하라</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20.1" customHeight="1" s="10">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Day</t>
@@ -3718,10 +3956,10 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="135" customHeight="1" s="8">
+    <row r="4" ht="135" customHeight="1" s="10">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>보강 1</t>
+          <t>Step 1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -3731,30 +3969,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>외부 OIDC 중앙 인증 연동 (엔터프라이즈 SSO)</t>
+          <t>RHBK 기반 외부 OIDC 중앙 인증</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1. RHOAI 3.x 인증 구조 이해(내장 vs 외부 OIDC)
-2. 외부 OIDC IdP 준비(Keycloak/RH-SSO를 SNO에 배포 또는 기존 IdP)
-3. OpenShift OAuth ↔ OIDC IdP 연동 → RHOAI가 그 그룹 인식하도록 설정
-4. OIDC 그룹 → RHOAI admin/user 그룹 매핑 검증 (oc auth can-i)</t>
+          <t>1. RHBK 26.6 Operator 설치
+2. 별도 PostgreSQL·TLS·Keycloak CR 구성
+3. KeycloakRealmImport로 realm/client/group/user 선언
+4. OpenShift OAuth에 RHBK OpenID IdP 추가, 기존 htpasswd 유지
+5. groups claim → OpenShift Group → RHOAI admin/user 권한 검증
+6. OAuth와 RHBK 리소스 원복</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>외부 IdP 로그인 + 그룹 기반 RHOAI 접근</t>
+          <t>RHBK 로그인 + 그룹 claim 기반 RHOAI 접근·관리자 권한</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>"사내 SSO(AD/Keycloak)로 RHOAI 로그인·권한을 통합해주세요"</t>
+          <t>"사내 SSO(AD/RHBK)로 RHOAI 로그인과 권한을 통합해주세요"</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>홈 SNO (CPU) — Keycloak도 SNO에</t>
+          <t>홈 SNO (CPU) + RHBK 26.6</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -3769,14 +4009,14 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>공식 #10. 3.x 신 인증구조. 거의 모든 엔터프라이즈 설치 필수. Day9 RBAC와 연계</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="135" customHeight="1" s="8">
+          <t>RHBK Operator는 DB를 관리하지 않는다. 실습은 단일 PostgreSQL/self-signed TLS, 운영은 외부 HA DB/조직 CA 사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="135" customHeight="1" s="10">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>보강 2</t>
+          <t>Step 2</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -3786,26 +4026,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>RHOAI 백업·복구 (구성/데이터 보호, DR)</t>
+          <t>OADP 1.6 기반 애플리케이션 백업·복구</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1. 백업 대상 식별: DSCI/DSC 구성, 파이프라인 메타DB, 모델레지스트리 DB, PVC, 사용자 리소스
-2. 리소스 백업(oc get -o yaml / etcd) + (선택) OADP/Velero로 ns·PVC 백업
-3. 백업 저장소 = 홈 TrueNAS S3
-4. OADP Operator는 현재 미러 카탈로그에 없으면 재미러 후 설치
-5. 복구 리허설: 리소스 삭제 후 복원 검증</t>
+          <t>1. OADP Operator와 DPA 구성
+2. TrueNAS MinIO S3 BackupStorageLocation 연결
+3. Kopia FSB로 Namespace·NFS PVC 백업
+4. Namespace 삭제 후 Restore와 checksum 검증
+5. DSCI/DSC/DashboardConfig 정적 export
+6. OADP와 etcd/Operator DR 경계 구분</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>백업 아티팩트 + 복구 리허설 성공</t>
+          <t>S3 backup + Namespace/PVC 복구 + 구성 export</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>"RHOAI/모델/파이프라인을 백업하고 장애 시 복구(DR)하려면?"</t>
+          <t>"RHOAI 사용자 리소스와 데이터를 백업하고 장애 시 복구하려면?"</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3825,14 +4066,14 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>공식 #11. TrueNAS S3는 backup location 후보. OADP 패키지가 현재 카탈로그에 없으면 보강 전 재미러 필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="135" customHeight="1" s="8">
+          <t>OCP 4.22는 OADP 1.6 사용. OADP는 전체 cluster/etcd/Operator DR을 대신하지 않음</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="135" customHeight="1" s="10">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>보강 3</t>
+          <t>Step 3</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3842,32 +4083,31 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>분산 워크로드 — Ray/KubeRay + Red Hat build of Kueue 연동</t>
+          <t>Ray/KubeRay + Red Hat build of Kueue 분산 workload</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1. Red Hat build of Kueue Operator 설치 및 DSC kueue=Unmanaged 확인
-2. RHOAI 분산 워크로드 컴포넌트 활성화(ray/trainingoperator 등 실제 CRD 확인)
-3. codeflare-sdk 또는 RayJob으로 소규모 분산 잡 제출
-4. Kueue LocalQueue 경유 및 워크로드 상태 확인
-5. JobSet/LWS는 카탈로그 추가 후 보강</t>
+          <t>1. DSC ray=Managed로 KubeRay 활성화
+2. Kueue ResourceFlavor/ClusterQueue/LocalQueue 구성
+3. CPU node head + GPU node worker RayJob 제출
+4. Workload admission, Pod node 배치, Ray 결과 검증
+5. RayJob 삭제 후 DSC ray 원복</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>분산 잡 완료 + Kueue 큐잉 관측</t>
+          <t>멀티노드 RayJob 완료 + Kueue admission 관측</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>"대규모 모델을 여러 노드/GPU로 분산훈련하려면?"</t>
+          <t>"전처리·튜닝 workload를 여러 노드로 분산하고 queue로 통제하려면?"</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>★멀티리소스(GPU 권장)
-SNO=CPU 소규모 로직만, 실분산=GPU 랩</t>
+          <t>홈 SNO + CPU/GPU worker (GPU 연산은 불필요)</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -3882,14 +4122,14 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>RHOAI 3.x에서 CodeFlare Operator는 제거 방향. KubeRay/Ray와 Red Hat build of Kueue 중심으로 보정</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="135" customHeight="1" s="8">
+          <t>CodeFlare Operator 별도 설치 없음. RHOAI KubeRay와 외부 Kueue 사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="135" customHeight="1" s="10">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>보강 4</t>
+          <t>Step 4</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -3899,25 +4139,26 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>관측성(Observability) 심화 + 감사(Audit) 로그</t>
+          <t>관측성 심화와 API 감사 로그</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1. (관측성) 분산워크로드/리소스 사용 메트릭, RHOAI 컴포넌트 상태 모니터링 (Day13 UWM 확장)
-2. 대시보드/알림 보강
-3. (감사) OpenShift audit log에서 RHOAI 리소스 변경·접근 추적(누가 무엇을 배포/삭제)
-4. 로그 조회·필터 + 컴플라이언스 보고용 추출</t>
+          <t>1. Kueue pending/admitted와 RHOAI Deployment metric 조회
+2. recording/alert PrometheusRule 생성
+3. Thanos API를 임시 SA token으로 조회
+4. ConfigMap·HardwareProfile 변경 이벤트 생성
+5. kube-apiserver audit log에서 user/verb/resource/code 추출</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>운영 대시보드 보강 + 감사 추적 시연</t>
+          <t>운영 metric/rule + 감사 JSONL 추적</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>"누가 무엇을 했는지 추적(감사)하고 운영 가시성을 갖추려면?(규제)"</t>
+          <t>"누가 어떤 RHOAI 리소스를 변경했고 운영 병목은 어디인지 추적하려면?"</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3937,14 +4178,14 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>공식 #12+#13. Day13(모니터링)과 합쳐 운영 완성. 규제 금융/공공 필수</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="135" customHeight="1" s="8">
+          <t>Day13 UWM 확장. 인증서 kubeconfig는 oc whoami -t 대신 임시 SA token 사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="135" customHeight="1" s="10">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>보강 5</t>
+          <t>Step 5</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3954,29 +4195,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Kueue 운영 — 대시보드 활성화·트러블슈팅·Red Hat build of Kueue 운영</t>
+          <t>Kueue 운영과 admission 트러블슈팅</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1. 대시보드에서 Kueue(워크로드 큐) 활성화·가시화
-2. 큐 적체/admit 실패 트러블슈팅(workload 상태·이벤트·쿼터 초과 진단)
-3. RHOAI DSC kueue=Unmanaged 상태에서 Red Hat build of Kueue Operator가 controller를 소유하는 구조 확인</t>
+          <t>1. DSC Unmanaged/외부 Kueue Managed 소유권 확인
+2. Dashboard disableKueue=false 확인
+3. CPU quota 부족 Job으로 admission 실패 재현
+4. Workload condition/event/metric 판정
+5. quota 확장 후 재입장·완료 검증
+6. Queue와 Dashboard flag 원복</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Kueue 운영·진단 + RHOAI 연동 체크리스트</t>
+          <t>Kueue 병목 계층 판정 + quota 변경 복구</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>"Kueue 잡이 안 도는데 진단·운영은? RHOAI와 외부 Kueue Operator 소유권은 어떻게 나누나요?"</t>
+          <t>"Kueue Job이 멈췄을 때 queue와 scheduler 중 어디를 진단해야 하나요?"</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>홈 SNO (CPU, Kueue 로직)</t>
+          <t>홈 SNO (CPU)</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -3991,14 +4235,14 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>공식 #8. 내장 Kueue 마이그레이션 실습이 아니라 RHOAI 3.x의 외부 Kueue Operator 연동/운영 실습으로 보정</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="135" customHeight="1" s="8">
+          <t>Generic Job은 RHOAI Dashboard Jobs 목록에 반드시 표시되지 않음. CLI Workload가 정본</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="135" customHeight="1" s="10">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>보강 6</t>
+          <t>Step 6</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -4008,24 +4252,26 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>플랫폼/대시보드 커스터마이징 (앱 타일·프로젝트범위·컴포넌트 리소스)</t>
+          <t>Dashboard·프로젝트·컴포넌트 커스터마이징</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1. (대시보드 앱) OdhApplication/OdhDashboardConfig로 앱 타일 활성/비활성 + 사내 도구 커스텀 타일 추가
-2. (프로젝트 범위) 특정 프로젝트에만 워크벤치이미지/HW프로파일/서빙런타임 노출
-3. (컴포넌트 리소스) RHOAI 컴포넌트 CPU/메모리 요청·제한 조정 → 저사양 SNO 경량화</t>
+          <t>1. OdhApplication으로 Gitea launcher tile 추가
+2. 프로젝트 범위 HardwareProfile 생성·가시성 확인
+3. rhods-dashboard container resource 소폭 조정
+4. Operator reconcile 후 유지 확인
+5. Step0 JSON으로 resource와 flag 정확히 원복</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>커스텀 대시보드 + 프로젝트범위 리소스 + 컴포넌트 리소스 조정</t>
+          <t>사내 앱 타일 + project HardwareProfile + component resource 변경·복구</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>"대시보드에 사내 도구를 노출하고, 팀별로 다른 리소스를? 저사양에 맞게 RHOAI를 가볍게?"</t>
+          <t>"사내 도구를 노출하고 팀별 profile과 플랫폼 resource를 관리하려면?"</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4045,14 +4291,14 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>공식 #3+#4+#6. ★앱=서빙모델 아님, 대시보드 런처 타일. 저사양 SNO엔 컴포넌트 다운튜닝이 실익</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="135" customHeight="1" s="8">
+          <t>opendatahub.io/managed=true를 임의로 false/제거하지 않음. 공식 customization 경계 준수</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="135" customHeight="1" s="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>보강 7</t>
+          <t>Step 7</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -4062,30 +4308,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>사용자/클러스터 추가 리소스 할당·확장</t>
+          <t>사용자 quota와 on-prem worker 확장 판단</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1. 사용자에게 추가 리소스 할당(쿼터/노드 리소스)
-2. (멀티노드) MachineSet/머신풀로 워커 추가 스케일 개념
-3. SNO 한계 인식 → 워커노드 추가(에이전트 ISO + CSR 승인) 시나리오 (홈서버 §6 연계)</t>
+          <t>1. node allocatable/requests/실사용 기준선
+2. ResourceQuota·LimitRange 기본값 주입
+3. 직접 Pod로 LimitRange max 거부와 ResourceQuota 집계 초과 재현
+4. platform None/MachineSet 없음 판정
+5. oc adm node-image ISO·CSR 승인 절차 설계
+6. SNO worker 추가와 control plane HA의 차이 정리</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>리소스 할당·확장 절차 이해</t>
+          <t>팀 quota 정책 + 확장 방식 판정표 + Agent ISO/CSR 절차</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>"사용자가 늘어 리소스가 부족한데 확장하려면?"</t>
+          <t>"사용자 증가로 resource가 부족할 때 quota와 cluster를 어떻게 확장하나요?"</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>홈 SNO(개념)
-실확장=멀티노드 필요</t>
+          <t>홈 SNO (quota 실습) / spare host 필요 시 실제 확장</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -4100,7 +4348,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>공식 #5. SNO 단일노드라 개념 위주. 홈서버 워커노드 추가와 연계</t>
+          <t>현재 홈랩은 MachineSet 대상이 아님. 실제 node 추가 없이 명령·CSR 판정까지만 검증</t>
         </is>
       </c>
     </row>

--- a/RHOAI-study-materials/2-RHOAI-Enablement-materials/RHOAI-HandsOn-v1.1/RHOAI-3.4-HandsOn-커리큘럼-v1.1.xlsx
+++ b/RHOAI-study-materials/2-RHOAI-Enablement-materials/RHOAI-HandsOn-v1.1/RHOAI-3.4-HandsOn-커리큘럼-v1.1.xlsx
@@ -563,7 +563,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02 (v1.0 기반 / 공식 문서·홈랩 미러 카탈로그 검증 반영)</t>
+          <t>2026-07-02 (v1.0 기반 / 공식 문서·disconnected 검증 환경 미러 카탈로그 반영)</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>★ 홈랩 disconnected OCP 4.22. 메인 테스트 = SNO + GPU worker + CPU worker. 공식 RHOAI 3.4 설치문서의 OCP 지원 범위와 다를 수 있어 트러블슈팅 훈련 조건으로 둠</t>
+          <t>★ 검증 환경: disconnected OCP 4.22, SNO + GPU worker + CPU worker. 공식 RHOAI 3.4 설치문서의 OCP 지원 범위와 다를 수 있어 트러블슈팅 훈련 조건으로 둠</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>홈랩 GPU worker 사용 가능. Day11-12,14와 추가 Week4/Week6은 GPU Operator/NFD/KMM 설치 후 수행하며, Week6은 동일 worker의 물리 GPU 2장이 필요. Week7 Ray는 CPU 연산으로 멀티노드 배치만 검증</t>
+          <t>검증 환경에서 GPU worker 사용 가능. Day11-12,14와 추가 Week4/Week6은 GPU Operator/NFD/KMM 설치 후 수행하며, Week6은 동일 worker의 물리 GPU 2장이 필요. Week7 Ray는 CPU 연산으로 멀티노드 배치만 검증</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>airgap/데모랩 → 홈랩 disconnected OCP 4.22(SNO+GPU worker+CPU worker) 기준, GPU는 홈랩 우선</t>
+          <t>airgap/데모랩 → disconnected OCP 4.22 검증 환경(SNO+GPU worker+CPU worker) 기준, GPU 실습 우선</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
     <row r="1" ht="17.25" customHeight="1" s="10">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>v0.9 → v1.1(설치·RawDeployment·홈랩 disconnected 보정) 변경점</t>
+          <t>v0.9 → v1.1(설치·RawDeployment·disconnected 검증 환경 보정) 변경점</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>홈랩 disconnected OCP 4.22(SNO+GPU worker+CPU worker) 기준, 공식 지원 범위 차이는 트러블슈팅 조건으로 명시</t>
+          <t>disconnected OCP 4.22 검증 환경(SNO+GPU worker+CPU worker) 기준, 공식 지원 범위 차이는 트러블슈팅 조건으로 명시</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>사용자 홈랩 실제 환경 반영. v1.0의 connected SNO 전제 보정</t>
+          <t>실제 검증 환경 반영. v1.0의 connected SNO 전제 보정</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>동료 v0.9의 강점은 유지하되 현재 홈랩과 공식문서 기준으로 실행 가능성 보정</t>
+          <t>동료 v0.9의 강점은 유지하되 검증 환경과 공식문서 기준으로 실행 가능성 보정</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>RHOAI 3.4 지원 범위와 현재 홈랩에서 직접 검증한 구성에 맞춤</t>
+          <t>RHOAI 3.4 지원 범위와 직접 검증한 환경 구성에 맞춤</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>미러·GPU·리소스 제약이 있는 홈랩에서도 반복 가능한 실습 결과를 우선</t>
+          <t>미러·GPU·리소스 제약이 있는 disconnected 검증 환경에서도 반복 가능한 실습 결과를 우선</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>RHOAI 3.4/OCP 4.22 공식 API와 현재 platform=None 홈랩 조건에 맞춰 운영자 runbook으로 구체화</t>
+          <t>RHOAI 3.4/OCP 4.22 공식 API와 platform=None 검증 환경 조건에 맞춰 운영자 runbook으로 구체화</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1196,7 @@
     <row r="1" ht="17.25" customHeight="1" s="10">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>Week 1: 설치 + 기본 서빙 (홈랩 disconnected / SNO+workers) — "빈 클러스터에 RHOAI를 올리고 첫 모델을 RawDeployment로 서빙하라"</t>
+          <t>Week 1: 설치 + 기본 서빙 (disconnected 검증 환경 / SNO+workers) — "빈 클러스터에 RHOAI를 올리고 첫 모델을 RawDeployment로 서빙하라"</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>홈랩 disconnected
+          <t>disconnected 검증 환경
 SNO+workers</t>
         </is>
       </c>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>홈랩 GPU worker</t>
+          <t>검증 환경 GPU worker</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>CPU Kueue=홈랩 / Time-Slicing=GPU worker</t>
+          <t>CPU Kueue=검증 구성 / Time-Slicing=GPU worker</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -3246,7 +3246,8 @@
           <t>1. Argo CD private repository Secret과 Application 3개 생성
 2. Tekton CI/promotion Pipeline과 EventListener 생성
 3. 수동 PipelineRun으로 단계별 검증
-4. Gitea main push webhook 연결</t>
+4. Gitea main push webhook 연결
+5. 새 commit push로 자동 PipelineRun 생성과 source-revision 검증</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -4348,7 +4349,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>현재 홈랩은 MachineSet 대상이 아님. 실제 node 추가 없이 명령·CSR 판정까지만 검증</t>
+          <t>검증 환경은 MachineSet 대상이 아님. 실제 node 추가 없이 명령·CSR 판정까지만 검증</t>
         </is>
       </c>
     </row>
